--- a/171/food/2026-01-23-sm.xlsx
+++ b/171/food/2026-01-23-sm.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>23.01.2026</t>
         </is>
       </c>
     </row>
@@ -932,33 +932,29 @@
           <t>гор.блюдо</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
+      <c r="C4" s="19" t="e"/>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Рис отварной</t>
+          <t>Котлета куриная</t>
         </is>
       </c>
       <c r="E4" s="21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F4" s="22" t="n">
         <v>18.35</v>
       </c>
-      <c r="G4" s="42" t="n">
-        <v>126.2</v>
+      <c r="G4" s="21" t="n">
+        <v>218</v>
       </c>
       <c r="H4" s="42" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="I4" s="42" t="n">
-        <v>3.6</v>
+        <v>12.6</v>
       </c>
       <c r="J4" s="43" t="n">
-        <v>24.5</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
@@ -970,31 +966,31 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>304</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Котлета куриная</t>
+          <t>Рис отварной №304</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>12.85</v>
       </c>
-      <c r="G5" s="44" t="n">
-        <v>210.4</v>
+      <c r="G5" s="28" t="n">
+        <v>130</v>
       </c>
       <c r="H5" s="44" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="44" t="n">
-        <v>12.6</v>
+        <v>3.6</v>
       </c>
       <c r="J5" s="45" t="n">
-        <v>19.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
@@ -1011,7 +1007,7 @@
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Чай с лимоном</t>
+          <t>Чай с лимоном №459</t>
         </is>
       </c>
       <c r="E6" s="28" t="n">
@@ -1020,8 +1016,8 @@
       <c r="F6" s="29" t="n">
         <v>33.04</v>
       </c>
-      <c r="G6" s="44" t="n">
-        <v>35.1</v>
+      <c r="G6" s="28" t="n">
+        <v>35</v>
       </c>
       <c r="H6" s="32" t="e"/>
       <c r="I6" s="44" t="n">
@@ -1038,11 +1034,7 @@
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
+      <c r="C7" s="27" t="e"/>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
@@ -1054,8 +1046,8 @@
       <c r="F7" s="29" t="n">
         <v>9.18</v>
       </c>
-      <c r="G7" s="44" t="n">
-        <v>116.9</v>
+      <c r="G7" s="28" t="n">
+        <v>121</v>
       </c>
       <c r="H7" s="44" t="n">
         <v>3.9</v>
@@ -1081,7 +1073,7 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="E8" s="28" t="n">
@@ -1090,8 +1082,8 @@
       <c r="F8" s="29" t="n">
         <v>18.35</v>
       </c>
-      <c r="G8" s="44" t="n">
-        <v>73.59999999999999</v>
+      <c r="G8" s="28" t="n">
+        <v>76</v>
       </c>
       <c r="H8" s="44" t="n">
         <v>1.2</v>
@@ -1154,14 +1146,34 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="27" t="e"/>
-      <c r="D12" s="26" t="e"/>
-      <c r="E12" s="32" t="e"/>
-      <c r="F12" s="32" t="e"/>
-      <c r="G12" s="32" t="e"/>
-      <c r="H12" s="32" t="e"/>
-      <c r="I12" s="32" t="e"/>
-      <c r="J12" s="33" t="e"/>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Суп гороховый №127</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>98</v>
+      </c>
+      <c r="H12" s="44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I12" s="44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J12" s="45" t="n">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="e"/>
@@ -1171,13 +1183,29 @@
         </is>
       </c>
       <c r="C13" s="27" t="e"/>
-      <c r="D13" s="26" t="e"/>
-      <c r="E13" s="32" t="e"/>
-      <c r="F13" s="32" t="e"/>
-      <c r="G13" s="32" t="e"/>
-      <c r="H13" s="32" t="e"/>
-      <c r="I13" s="32" t="e"/>
-      <c r="J13" s="33" t="e"/>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Котлета куриная</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>282</v>
+      </c>
+      <c r="H13" s="44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I13" s="44" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>25.3</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="25" t="e"/>
@@ -1186,14 +1214,34 @@
           <t>гарнир</t>
         </is>
       </c>
-      <c r="C14" s="27" t="e"/>
-      <c r="D14" s="26" t="e"/>
-      <c r="E14" s="32" t="e"/>
-      <c r="F14" s="32" t="e"/>
-      <c r="G14" s="32" t="e"/>
-      <c r="H14" s="32" t="e"/>
-      <c r="I14" s="32" t="e"/>
-      <c r="J14" s="33" t="e"/>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Рис отварной №304</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>210</v>
+      </c>
+      <c r="H14" s="44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" s="44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J14" s="45" t="n">
+        <v>36.7</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="25" t="e"/>
@@ -1202,14 +1250,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="27" t="e"/>
-      <c r="D15" s="26" t="e"/>
-      <c r="E15" s="32" t="e"/>
-      <c r="F15" s="32" t="e"/>
-      <c r="G15" s="32" t="e"/>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>180</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>35</v>
+      </c>
       <c r="H15" s="32" t="e"/>
-      <c r="I15" s="32" t="e"/>
-      <c r="J15" s="33" t="e"/>
+      <c r="I15" s="44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="45" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="25" t="e"/>
@@ -1219,13 +1285,29 @@
         </is>
       </c>
       <c r="C16" s="27" t="e"/>
-      <c r="D16" s="26" t="e"/>
-      <c r="E16" s="32" t="e"/>
-      <c r="F16" s="32" t="e"/>
-      <c r="G16" s="32" t="e"/>
-      <c r="H16" s="32" t="e"/>
-      <c r="I16" s="32" t="e"/>
-      <c r="J16" s="33" t="e"/>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>187</v>
+      </c>
+      <c r="H16" s="44" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I16" s="44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" s="45" t="n">
+        <v>38.6</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="25" t="e"/>
